--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2c2164018b724295"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc793a5d4557547b5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc793a5d4557547b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2f77911335ca480b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2f77911335ca480b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcc215c91a79349e9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcc215c91a79349e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4efb0bacc3674ab9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4efb0bacc3674ab9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R291e0e61c3bc4d12"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R291e0e61c3bc4d12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R36bb91bc1cd94dd8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R36bb91bc1cd94dd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2c1c244754454dd1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2c1c244754454dd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb8866add79114762"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb8866add79114762"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R70d1b95df93e4218"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R70d1b95df93e4218"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R90d33fed89504a03"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R90d33fed89504a03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd05c210d4e014972"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd05c210d4e014972"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc067c93b154a4ea5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc067c93b154a4ea5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R30312506b7334a55"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R30312506b7334a55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6453085c991740f5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6453085c991740f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra7650cd088c54f7f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra7650cd088c54f7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R93b856cb6f924608"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R93b856cb6f924608"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra9e97f898b1f4b20"/>
   </x:sheets>
 </x:workbook>
 </file>
